--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$131</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4060" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -891,6 +891,12 @@
   </si>
   <si>
     <t>ParticipantRole.code</t>
+  </si>
+  <si>
+    <t>Organizer.participant.participantRole.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>ParticipantRole.sdtcSpecialty</t>
   </si>
   <si>
     <t>Organizer.participant.participantRole.addr</t>
@@ -1554,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK130"/>
+  <dimension ref="A1:AK131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.328125" customWidth="true" bestFit="true"/>
@@ -9939,7 +9945,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9992,7 +9998,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10012,10 +10018,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10038,7 +10044,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10091,7 +10097,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10111,10 +10117,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10125,7 +10131,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -10137,7 +10143,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10190,13 +10196,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -10210,10 +10216,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10221,7 +10227,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>75</v>
@@ -10236,7 +10242,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10289,7 +10295,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10309,20 +10315,18 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>75</v>
@@ -10337,12 +10341,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>85</v>
+        <v>296</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10368,11 +10370,13 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10390,7 +10394,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>89</v>
+        <v>297</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10410,21 +10414,23 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10436,11 +10442,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10467,13 +10473,11 @@
         <v>74</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10491,13 +10495,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10511,10 +10515,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10525,7 +10529,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>74</v>
@@ -10537,11 +10541,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10592,19 +10596,19 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>74</v>
@@ -10612,18 +10616,16 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
@@ -10640,11 +10642,11 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10671,11 +10673,13 @@
         <v>74</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>74</v>
@@ -10693,7 +10697,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10705,7 +10709,7 @@
         <v>74</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>74</v>
@@ -10713,17 +10717,17 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>80</v>
@@ -10741,11 +10745,11 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10772,13 +10776,11 @@
         <v>74</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -10796,7 +10798,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10816,17 +10818,17 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>80</v>
@@ -10844,11 +10846,11 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10899,7 +10901,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10919,20 +10921,20 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>75</v>
@@ -10947,11 +10949,11 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -10960,7 +10962,7 @@
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>74</v>
@@ -11002,7 +11004,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11022,17 +11024,17 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>75</v>
@@ -11050,11 +11052,11 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11063,7 +11065,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>74</v>
@@ -11105,7 +11107,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11125,21 +11127,23 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11151,11 +11155,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11206,13 +11210,13 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>74</v>
@@ -11226,10 +11230,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11240,7 +11244,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11252,21 +11256,23 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
-        <v>306</v>
+        <v>74</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>307</v>
+        <v>74</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>74</v>
@@ -11281,11 +11287,13 @@
         <v>74</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y96" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z96" t="s" s="2">
-        <v>308</v>
+        <v>74</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>74</v>
@@ -11303,13 +11311,13 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>309</v>
+        <v>125</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>74</v>
@@ -11323,10 +11331,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11356,14 +11364,14 @@
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>74</v>
+        <v>308</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>311</v>
+        <v>74</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>74</v>
+        <v>309</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>74</v>
@@ -11382,7 +11390,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11400,7 +11408,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11420,10 +11428,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11446,7 +11454,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>253</v>
+        <v>85</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11457,7 +11465,7 @@
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>74</v>
@@ -11475,29 +11483,29 @@
         <v>74</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11517,10 +11525,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11531,7 +11539,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -11543,7 +11551,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11572,13 +11580,11 @@
         <v>74</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11596,13 +11602,13 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
@@ -11616,10 +11622,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11642,7 +11648,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11695,7 +11701,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11715,10 +11721,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11729,7 +11735,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
@@ -11741,12 +11747,10 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -11796,13 +11800,13 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
@@ -11816,10 +11820,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11842,10 +11846,12 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>173</v>
+        <v>326</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -11941,7 +11947,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -11994,7 +12000,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12014,10 +12020,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12028,7 +12034,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>74</v>
@@ -12040,7 +12046,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12093,13 +12099,13 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>74</v>
@@ -12309,7 +12315,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>338</v>
       </c>
@@ -12322,13 +12328,13 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>74</v>
@@ -12339,9 +12345,7 @@
       <c r="K107" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12410,28 +12414,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E108" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>74</v>
@@ -12440,12 +12442,12 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L108" s="2"/>
-      <c r="M108" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12471,11 +12473,13 @@
         <v>74</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12493,13 +12497,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>89</v>
+        <v>340</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12513,21 +12517,23 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>74</v>
@@ -12539,11 +12545,11 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12570,13 +12576,11 @@
         <v>74</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12594,13 +12598,13 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>74</v>
@@ -12614,10 +12618,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12628,7 +12632,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12640,11 +12644,11 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12695,19 +12699,19 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>74</v>
@@ -12715,18 +12719,16 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E111" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
@@ -12743,11 +12745,11 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12774,11 +12776,13 @@
         <v>74</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>74</v>
@@ -12796,7 +12800,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12808,7 +12812,7 @@
         <v>74</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>74</v>
@@ -12816,17 +12820,17 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>80</v>
@@ -12844,11 +12848,11 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12875,13 +12879,11 @@
         <v>74</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -12899,7 +12901,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12919,17 +12921,17 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F113" t="s" s="2">
         <v>80</v>
@@ -12947,11 +12949,11 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13002,7 +13004,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13022,20 +13024,20 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>75</v>
@@ -13050,11 +13052,11 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13063,7 +13065,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>74</v>
@@ -13105,7 +13107,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13125,17 +13127,17 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>75</v>
@@ -13153,11 +13155,11 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13166,7 +13168,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>74</v>
@@ -13208,7 +13210,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13228,21 +13230,23 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F116" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>74</v>
@@ -13254,11 +13258,11 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13309,13 +13313,13 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>74</v>
@@ -13329,10 +13333,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13343,7 +13347,7 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>74</v>
@@ -13355,14 +13359,16 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
+      <c r="M117" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
-        <v>351</v>
+        <v>74</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
@@ -13384,11 +13390,13 @@
         <v>74</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y117" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z117" t="s" s="2">
-        <v>352</v>
+        <v>74</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>74</v>
@@ -13406,13 +13414,13 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>353</v>
+        <v>125</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>74</v>
@@ -13426,10 +13434,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13452,60 +13460,58 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>74</v>
+        <v>353</v>
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y118" s="2"/>
+      <c r="Z118" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13525,10 +13531,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13551,7 +13557,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>358</v>
+        <v>107</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13562,7 +13568,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>74</v>
+        <v>357</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>74</v>
@@ -13604,7 +13610,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13624,10 +13630,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13650,7 +13656,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13749,7 +13755,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -13802,7 +13808,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -13822,10 +13828,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13848,7 +13854,7 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -13901,7 +13907,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -13921,10 +13927,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13947,7 +13953,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14000,7 +14006,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14020,10 +14026,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14046,7 +14052,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14099,7 +14105,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14119,10 +14125,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14145,7 +14151,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14198,7 +14204,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14218,10 +14224,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14244,7 +14250,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14297,7 +14303,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14317,10 +14323,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14343,7 +14349,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14396,7 +14402,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14416,10 +14422,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14442,7 +14448,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14495,7 +14501,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14515,10 +14521,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14541,7 +14547,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14594,7 +14600,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14614,10 +14620,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14640,7 +14646,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -14693,26 +14699,125 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AG130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK130" t="s" s="2">
+      <c r="B131" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK131" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK130">
+  <autoFilter ref="A1:AK131">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14722,7 +14827,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI129">
+  <conditionalFormatting sqref="A2:AI130">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
